--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.72774968068918</v>
+        <v>4.668259323111992</v>
       </c>
       <c r="D2" t="n">
-        <v>28.55695263742088</v>
+        <v>4.640504803580894</v>
       </c>
       <c r="E2" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F2" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.71695400828181</v>
+        <v>6.129005026345794</v>
       </c>
       <c r="D3" t="n">
-        <v>37.81564770666571</v>
+        <v>6.145042752333178</v>
       </c>
       <c r="E3" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F3" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.05693621691413</v>
+        <v>2.771752135248546</v>
       </c>
       <c r="D4" t="n">
-        <v>16.99608464888277</v>
+        <v>2.76186375544345</v>
       </c>
       <c r="E4" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F4" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.68578299854394</v>
+        <v>4.173939737263391</v>
       </c>
       <c r="D5" t="n">
-        <v>25.34632362826771</v>
+        <v>4.118777589593503</v>
       </c>
       <c r="E5" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F5" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.18616708770308</v>
+        <v>7.342752151751752</v>
       </c>
       <c r="D6" t="n">
-        <v>44.8581647323846</v>
+        <v>7.289451769012498</v>
       </c>
       <c r="E6" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F6" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.17757897816133</v>
+        <v>2.466356583951217</v>
       </c>
       <c r="D7" t="n">
-        <v>15.49786028114478</v>
+        <v>2.518402295686027</v>
       </c>
       <c r="E7" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F7" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.03434463128698</v>
+        <v>4.880581002584134</v>
       </c>
       <c r="D8" t="n">
-        <v>30.17922608956727</v>
+        <v>4.90412423955468</v>
       </c>
       <c r="E8" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F8" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.03130099147236</v>
+        <v>6.180086411114259</v>
       </c>
       <c r="D9" t="n">
-        <v>38.03869505375513</v>
+        <v>6.181287946235209</v>
       </c>
       <c r="E9" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F9" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.37477135412661</v>
+        <v>8.023400345045575</v>
       </c>
       <c r="D10" t="n">
-        <v>49.70093950960862</v>
+        <v>8.076402670311401</v>
       </c>
       <c r="E10" t="n">
-        <v>11.08269227154714</v>
+        <v>1.80093749412641</v>
       </c>
       <c r="F10" t="n">
-        <v>11.08406855222478</v>
+        <v>1.801161139736527</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
